--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.8100134768365603</v>
+        <v>1.138253994517384</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.1899865231634468</v>
+        <v>0.1382539945173897</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.03913651734483292</v>
+        <v>0.02483947476541637</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.0226864377851389</v>
+        <v>0.04238482975093061</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3094478643360692</v>
+        <v>0.2133268038140311</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.02225941700133418</v>
+        <v>0.151550405096308</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.03179331133464345</v>
+        <v>0.221622949246091</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.6326415980446234</v>
+        <v>0.3890992583208051</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.06186206766326553</v>
+        <v>0.06383840172971157</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2612196186573544</v>
+        <v>0.1679541035950467</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02551030999744871</v>
+        <v>0.2731799048407619</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5177533383216743</v>
+        <v>0.200191414347326</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2022年10月-2026年04月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>23.91719475274398</v>
+        <v>17.79825348476959</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.0954116696695505</v>
+        <v>0.07100168308781013</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2239056891339192</v>
+        <v>0.1719200771388294</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.169924812030075</v>
+        <v>7.66390977443609</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.138253994517384</v>
+        <v>0.7804455492162476</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.1382539945173897</v>
+        <v>-0.2195544507837593</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.02483947476541637</v>
+        <v>-0.04588272894193413</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.04238482975093061</v>
+        <v>-0.02954814520396953</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2133268038140311</v>
+        <v>0.2219753679375241</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.151550405096308</v>
+        <v>-0.1678336992763703</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.221622949246091</v>
+        <v>-0.2377386592475586</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.3890992583208051</v>
+        <v>0.4894202156074435</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06383840172971157</v>
+        <v>-0.09374914946042189</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.1679541035950467</v>
+        <v>0.1949225977902041</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2731799048407619</v>
+        <v>-0.1216022406642991</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.200191414347326</v>
+        <v>0.3840128048938107</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2022年10月-2026年04月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17.79825348476959</v>
+        <v>18.31665825790187</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07100168308781013</v>
+        <v>0.07306972933991256</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1719200771388294</v>
+        <v>0.1766356920668773</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7.66390977443609</v>
+        <v>2.846616541353383</v>
       </c>
     </row>
     <row r="24">
